--- a/tools/importer/reports/import-sage-product-page.report.xlsx
+++ b/tools/importer/reports/import-sage-product-page.report.xlsx
@@ -52,7 +52,7 @@
     <t>sage-product-page</t>
   </si>
   <si>
-    <t>2026-05-06T16:02:42.532Z</t>
+    <t>2026-05-07T08:36:23.869Z</t>
   </si>
   <si>
     <t>Sage Prevalon Air Pump - 120V | Stryker</t>

--- a/tools/importer/reports/import-sage-product-page.report.xlsx
+++ b/tools/importer/reports/import-sage-product-page.report.xlsx
@@ -52,7 +52,7 @@
     <t>sage-product-page</t>
   </si>
   <si>
-    <t>2026-05-07T08:36:23.869Z</t>
+    <t>2026-05-07T08:54:29.470Z</t>
   </si>
   <si>
     <t>Sage Prevalon Air Pump - 120V | Stryker</t>

--- a/tools/importer/reports/import-sage-product-page.report.xlsx
+++ b/tools/importer/reports/import-sage-product-page.report.xlsx
@@ -52,7 +52,7 @@
     <t>sage-product-page</t>
   </si>
   <si>
-    <t>2026-05-07T08:54:29.470Z</t>
+    <t>2026-05-07T10:57:28.484Z</t>
   </si>
   <si>
     <t>Sage Prevalon Air Pump - 120V | Stryker</t>

--- a/tools/importer/reports/import-sage-product-page.report.xlsx
+++ b/tools/importer/reports/import-sage-product-page.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
   <si>
     <t>_reportFile</t>
   </si>
@@ -59,6 +59,24 @@
   </si>
   <si>
     <t>https://www.stryker.com/us/en/sage/products/sage-air-pump.html</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-airtap-lc.report.json</t>
+  </si>
+  <si>
+    <t>["hcp-banner","hero","sticky-nav","columns-overview","cards","cards","cards","connect-banner","connect-banner","connect-banner","form","tabs-resources","columns-resources"]</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-airtap-lc</t>
+  </si>
+  <si>
+    <t>2026-05-07T14:32:39.371Z</t>
+  </si>
+  <si>
+    <t>Sage AirTAP LC Lift Compatible Patient Repositioning System | Stryker</t>
+  </si>
+  <si>
+    <t>https://www.stryker.com/us/en/sage/products/sage-airtap-lc.html</t>
   </si>
 </sst>
 </file>
@@ -447,16 +465,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="47" customWidth="1"/>
+    <col min="1" max="1" width="48" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="35" customWidth="1"/>
+    <col min="3" max="3" width="36" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="41" customWidth="1"/>
-    <col min="8" max="8" width="50" customWidth="1"/>
+    <col min="7" max="8" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -509,6 +526,32 @@
       </c>
       <c r="H2" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-sage-product-page.report.xlsx
+++ b/tools/importer/reports/import-sage-product-page.report.xlsx
@@ -70,7 +70,7 @@
     <t>us/en/sage/products/sage-airtap-lc</t>
   </si>
   <si>
-    <t>2026-05-07T14:32:39.371Z</t>
+    <t>2026-05-08T13:56:13.867Z</t>
   </si>
   <si>
     <t>Sage AirTAP LC Lift Compatible Patient Repositioning System | Stryker</t>

--- a/tools/importer/reports/import-sage-product-page.report.xlsx
+++ b/tools/importer/reports/import-sage-product-page.report.xlsx
@@ -64,13 +64,13 @@
     <t>us/en/sage/products/sage-airtap-lc.report.json</t>
   </si>
   <si>
-    <t>["hcp-banner","hero","sticky-nav","columns-overview","cards","cards","cards","connect-banner","connect-banner","connect-banner","form","tabs-resources","columns-resources"]</t>
+    <t>["hcp-banner","hero","sticky-nav","columns-overview","cards","cards","cards","did-you-know","connect-banner","connect-banner","form","tabs-resources","columns-resources"]</t>
   </si>
   <si>
     <t>us/en/sage/products/sage-airtap-lc</t>
   </si>
   <si>
-    <t>2026-05-08T13:56:13.867Z</t>
+    <t>2026-05-08T15:20:05.245Z</t>
   </si>
   <si>
     <t>Sage AirTAP LC Lift Compatible Patient Repositioning System | Stryker</t>

--- a/tools/importer/reports/import-sage-product-page.report.xlsx
+++ b/tools/importer/reports/import-sage-product-page.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="195">
   <si>
     <t>_reportFile</t>
   </si>
@@ -37,6 +37,30 @@
     <t>url</t>
   </si>
   <si>
+    <t>us/en/sage/urine-management.report.json</t>
+  </si>
+  <si>
+    <t>["hcp-banner","hero","sticky-nav","columns-overview","columns-overview","columns-overview","columns-overview","cards","cards","connect-banner","form","tabs-resources","columns-resources"]</t>
+  </si>
+  <si>
+    <t>us/en/sage/urine-management</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>sage-product-page</t>
+  </si>
+  <si>
+    <t>2026-05-11T14:43:12.196Z</t>
+  </si>
+  <si>
+    <t>External urine management devices for male and female anatomy | Stryker</t>
+  </si>
+  <si>
+    <t>https://www.stryker.com/us/en/sage/urine-management.html</t>
+  </si>
+  <si>
     <t>us/en/sage/products/sage-air-pump.report.json</t>
   </si>
   <si>
@@ -46,12 +70,6 @@
     <t>us/en/sage/products/sage-air-pump</t>
   </si>
   <si>
-    <t>success</t>
-  </si>
-  <si>
-    <t>sage-product-page</t>
-  </si>
-  <si>
     <t>2026-05-07T10:57:28.484Z</t>
   </si>
   <si>
@@ -64,19 +82,520 @@
     <t>us/en/sage/products/sage-airtap-lc.report.json</t>
   </si>
   <si>
-    <t>["hcp-banner","hero","sticky-nav","columns-overview","cards","cards","cards","did-you-know","connect-banner","connect-banner","form","tabs-resources","columns-resources"]</t>
+    <t>["hcp-banner","hero","sticky-nav","columns-overview","cards","cards","cards","did-you-know","faq-accordion","connect-banner","connect-banner","form","tabs-resources","columns-resources"]</t>
   </si>
   <si>
     <t>us/en/sage/products/sage-airtap-lc</t>
   </si>
   <si>
-    <t>2026-05-08T15:20:05.245Z</t>
+    <t>2026-05-11T11:25:39.690Z</t>
   </si>
   <si>
     <t>Sage AirTAP LC Lift Compatible Patient Repositioning System | Stryker</t>
   </si>
   <si>
     <t>https://www.stryker.com/us/en/sage/products/sage-airtap-lc.html</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-airtap-xxl.report.json</t>
+  </si>
+  <si>
+    <t>["hcp-banner","hero","sticky-nav","columns-overview","cards","connect-banner","form","tabs-resources","columns-resources"]</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-airtap-xxl</t>
+  </si>
+  <si>
+    <t>2026-05-11T14:36:46.596Z</t>
+  </si>
+  <si>
+    <t>Sage Prevalon AirTAP XXL Patient Repositioning System | Stryker</t>
+  </si>
+  <si>
+    <t>https://www.stryker.com/us/en/sage/products/sage-airtap-xxl.html</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-airtap.report.json</t>
+  </si>
+  <si>
+    <t>["hcp-banner","hero","sticky-nav","columns-overview","cards","did-you-know","faq-accordion","connect-banner","connect-banner","form","tabs-resources","columns-resources"]</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-airtap</t>
+  </si>
+  <si>
+    <t>2026-05-11T14:37:08.204Z</t>
+  </si>
+  <si>
+    <t>Sage Prevalon AirTAP Patient Repositioning System | Stryker</t>
+  </si>
+  <si>
+    <t>https://www.stryker.com/us/en/sage/products/sage-airtap.html</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-barrier-cream-cloths.report.json</t>
+  </si>
+  <si>
+    <t>["hcp-banner","hero","sticky-nav","columns-overview","cards","cards","faq-accordion","connect-banner","form","tabs-resources","columns-resources"]</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-barrier-cream-cloths</t>
+  </si>
+  <si>
+    <t>2026-05-11T14:37:20.060Z</t>
+  </si>
+  <si>
+    <t>Sage Comfort Shield Barrier Cream Cloths | Stryker</t>
+  </si>
+  <si>
+    <t>https://www.stryker.com/us/en/sage/products/sage-barrier-cream-cloths.html</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-bath-cloths.report.json</t>
+  </si>
+  <si>
+    <t>["hcp-banner","hero","sticky-nav","cards","cards","connect-banner","form","tabs-resources","columns-resources"]</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-bath-cloths</t>
+  </si>
+  <si>
+    <t>2026-05-11T14:37:33.144Z</t>
+  </si>
+  <si>
+    <t>Sage Bath Cloths | Stryker</t>
+  </si>
+  <si>
+    <t>https://www.stryker.com/us/en/sage/products/sage-bath-cloths.html</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-chg-cloths.report.json</t>
+  </si>
+  <si>
+    <t>["hcp-banner","hero","sticky-nav","cards","connect-banner","connect-banner","form","tabs-resources","columns-resources"]</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-chg-cloths</t>
+  </si>
+  <si>
+    <t>2026-05-11T14:37:46.042Z</t>
+  </si>
+  <si>
+    <t>Sage 2% Chlorhexidine Gluconate (CHG) Cloths | Stryker</t>
+  </si>
+  <si>
+    <t>https://www.stryker.com/us/en/sage/products/sage-chg-cloths.html</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-foot-and-leg-stabilizer-wedge.report.json</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-foot-and-leg-stabilizer-wedge</t>
+  </si>
+  <si>
+    <t>2026-05-11T14:37:58.168Z</t>
+  </si>
+  <si>
+    <t>Sage Prevalon Foot and Leg Stabilizer Wedge | Stryker</t>
+  </si>
+  <si>
+    <t>https://www.stryker.com/us/en/sage/products/sage-foot-and-leg-stabilizer-wedge.html</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-halfmats.report.json</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-halfmats</t>
+  </si>
+  <si>
+    <t>2026-05-11T14:38:11.530Z</t>
+  </si>
+  <si>
+    <t>Sage HalfMATS Mobile Air Transfer System | Stryker</t>
+  </si>
+  <si>
+    <t>https://www.stryker.com/us/en/sage/products/sage-halfmats.html</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-heel-protector-i.report.json</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-heel-protector-i</t>
+  </si>
+  <si>
+    <t>2026-05-11T14:38:21.229Z</t>
+  </si>
+  <si>
+    <t>Sage Prevalon Heel Protector I | Stryker</t>
+  </si>
+  <si>
+    <t>https://www.stryker.com/us/en/sage/products/sage-heel-protector-i.html</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-heel-protector-ii.report.json</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-heel-protector-ii</t>
+  </si>
+  <si>
+    <t>2026-05-11T14:38:34.747Z</t>
+  </si>
+  <si>
+    <t>Sage Prevalon Heel Protector II | Stryker</t>
+  </si>
+  <si>
+    <t>https://www.stryker.com/us/en/sage/products/sage-heel-protector-ii.html</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-heel-protector-iii.report.json</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-heel-protector-iii</t>
+  </si>
+  <si>
+    <t>2026-05-11T14:38:47.584Z</t>
+  </si>
+  <si>
+    <t>Sage Prevalon Heel Protector III | Stryker</t>
+  </si>
+  <si>
+    <t>https://www.stryker.com/us/en/sage/products/sage-heel-protector-iii.html</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-heel-protector-or.report.json</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-heel-protector-or</t>
+  </si>
+  <si>
+    <t>2026-05-11T14:38:59.971Z</t>
+  </si>
+  <si>
+    <t>Sage Heel Protector OR | Stryker</t>
+  </si>
+  <si>
+    <t>https://www.stryker.com/us/en/sage/products/sage-heel-protector-or.html</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-incontinence-clean-up-cloths.report.json</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-incontinence-clean-up-cloths</t>
+  </si>
+  <si>
+    <t>2026-05-11T14:39:10.898Z</t>
+  </si>
+  <si>
+    <t>Sage Incontinence Clean-up Cloths | Stryker</t>
+  </si>
+  <si>
+    <t>https://www.stryker.com/us/en/sage/products/sage-incontinence-clean-up-cloths.html</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-m-care.report.json</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-m-care</t>
+  </si>
+  <si>
+    <t>2026-05-11T14:39:34.165Z</t>
+  </si>
+  <si>
+    <t>Sage M-Care Meatal Cleansing Cloth | Stryker</t>
+  </si>
+  <si>
+    <t>https://www.stryker.com/us/en/sage/products/sage-m-care.html</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-m-microclimate-body-pads.report.json</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-m-microclimate-body-pads</t>
+  </si>
+  <si>
+    <t>2026-05-11T14:39:23.002Z</t>
+  </si>
+  <si>
+    <t>Sage M² Microclimate Body Pads | Stryker</t>
+  </si>
+  <si>
+    <t>https://www.stryker.com/us/en/sage/products/sage-m--microclimate-body-pads.html</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-mats.report.json</t>
+  </si>
+  <si>
+    <t>["hcp-banner","hero","sticky-nav","cards","cards","did-you-know","faq-accordion","connect-banner","connect-banner","form","tabs-resources","columns-resources"]</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-mats</t>
+  </si>
+  <si>
+    <t>2026-05-11T14:39:45.852Z</t>
+  </si>
+  <si>
+    <t>Sage Prevalon Mobile Air Transfer System (MATS) | Stryker</t>
+  </si>
+  <si>
+    <t>https://www.stryker.com/us/en/sage/products/sage-mats.html</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-multi-position-mats.report.json</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-multi-position-mats</t>
+  </si>
+  <si>
+    <t>2026-05-11T14:39:59.163Z</t>
+  </si>
+  <si>
+    <t>Sage Multi-Position MATS 2.0 Mobile Air Transfer System | Stryker</t>
+  </si>
+  <si>
+    <t>https://www.stryker.com/us/en/sage/products/sage-multi-position-mats.html</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-nose-to-toes.report.json</t>
+  </si>
+  <si>
+    <t>["hcp-banner","hero","sticky-nav","columns-overview","cards","cards","connect-banner","form","tabs-resources","columns-resources"]</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-nose-to-toes</t>
+  </si>
+  <si>
+    <t>2026-05-11T14:40:09.289Z</t>
+  </si>
+  <si>
+    <t>Sage Nose to Toes Pre-Op Prepping Systems | Stryker</t>
+  </si>
+  <si>
+    <t>https://www.stryker.com/us/en/sage/products/sage-nose-to-toes.html</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-oral-hygiene-systems-for-non-ventilated-patients.report.json</t>
+  </si>
+  <si>
+    <t>["hcp-banner","hero","sticky-nav","columns-overview","cards","cards","connect-banner","connect-banner","form","tabs-resources","columns-resources"]</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-oral-hygiene-systems-for-non-ventilated-patients</t>
+  </si>
+  <si>
+    <t>2026-05-11T14:40:22.208Z</t>
+  </si>
+  <si>
+    <t>Sage oral hygiene systems for non-ventilated patients | Stryker</t>
+  </si>
+  <si>
+    <t>https://www.stryker.com/us/en/sage/products/sage-oral-hygiene-systems-for-non-ventilated-patients.html</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-oral-hygiene-systems-for-ventilated-patients.report.json</t>
+  </si>
+  <si>
+    <t>["hcp-banner","hero","sticky-nav","columns-overview","columns-overview","cards","cards","cards","connect-banner","connect-banner","form","tabs-resources","columns-resources"]</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-oral-hygiene-systems-for-ventilated-patients</t>
+  </si>
+  <si>
+    <t>2026-05-11T14:40:33.054Z</t>
+  </si>
+  <si>
+    <t>Sage oral hygiene systems for ventilated patients | Stryker</t>
+  </si>
+  <si>
+    <t>https://www.stryker.com/us/en/sage/products/sage-oral-hygiene-systems-for-ventilated-patients.html</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-oral-hygiene-tools.report.json</t>
+  </si>
+  <si>
+    <t>["hcp-banner","hero","sticky-nav","columns-overview","connect-banner","connect-banner","form","tabs-resources","columns-resources"]</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-oral-hygiene-tools</t>
+  </si>
+  <si>
+    <t>2026-05-11T14:40:44.993Z</t>
+  </si>
+  <si>
+    <t>Sage oral hygiene tools | Stryker</t>
+  </si>
+  <si>
+    <t>https://www.stryker.com/us/en/sage/products/sage-oral-hygiene-tools.html</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-oral-solutions-and-moisturizers.report.json</t>
+  </si>
+  <si>
+    <t>["hcp-banner","hero","sticky-nav","connect-banner","form","tabs-resources","columns-resources"]</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-oral-solutions-and-moisturizers</t>
+  </si>
+  <si>
+    <t>2026-05-11T14:40:57.951Z</t>
+  </si>
+  <si>
+    <t>Sage oral solutions and moisturizers | Stryker</t>
+  </si>
+  <si>
+    <t>https://www.stryker.com/us/en/sage/products/sage-oral-solutions-and-moisturizers.html</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-primafit.report.json</t>
+  </si>
+  <si>
+    <t>["hcp-banner","hero","sticky-nav","cards","cards","faq-accordion","connect-banner","form","tabs-resources","columns-resources"]</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-primafit</t>
+  </si>
+  <si>
+    <t>2026-05-11T14:41:11.299Z</t>
+  </si>
+  <si>
+    <t>Sage PrimaFit External Urine Management for the Female Anatomy | Stryker</t>
+  </si>
+  <si>
+    <t>https://www.stryker.com/us/en/sage/products/sage-primafit.html</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-primofit.report.json</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-primofit</t>
+  </si>
+  <si>
+    <t>2026-05-11T14:41:21.948Z</t>
+  </si>
+  <si>
+    <t>Sage PrimoFit+ External Urine Management for the Male Anatomy | Stryker</t>
+  </si>
+  <si>
+    <t>https://www.stryker.com/us/en/sage/products/sage-primofit.html</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-rinse-free-shampoo-caps.report.json</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-rinse-free-shampoo-caps</t>
+  </si>
+  <si>
+    <t>2026-05-11T14:41:35.462Z</t>
+  </si>
+  <si>
+    <t>Sage Rinse-Free Shampoo Cap | Stryker</t>
+  </si>
+  <si>
+    <t>https://www.stryker.com/us/en/sage/products/sage-rinse-free-shampoo-caps.html</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-self-oral-care.report.json</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-self-oral-care</t>
+  </si>
+  <si>
+    <t>2026-05-11T14:41:47.588Z</t>
+  </si>
+  <si>
+    <t>Sage Self Oral Care Toothbrush with Corinz Antiseptic Cleansing and Moisturizing Oral Rinse | Stryker</t>
+  </si>
+  <si>
+    <t>https://www.stryker.com/us/en/sage/products/sage-self-oral-care.html</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-sps.report.json</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-sps</t>
+  </si>
+  <si>
+    <t>2026-05-11T14:41:59.135Z</t>
+  </si>
+  <si>
+    <t>Sage Prevalon Seated Positioning System (SPS) | Stryker</t>
+  </si>
+  <si>
+    <t>https://www.stryker.com/us/en/sage/products/sage-sps.html</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-tap-1-0.report.json</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-tap-1-0</t>
+  </si>
+  <si>
+    <t>2026-05-11T14:42:12.099Z</t>
+  </si>
+  <si>
+    <t>Sage Prevalon Turn and Position System (TAP) 1.0 | Stryker</t>
+  </si>
+  <si>
+    <t>https://www.stryker.com/us/en/sage/products/sage-tap-1-0.html</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-tap-2-0.report.json</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-tap-2-0</t>
+  </si>
+  <si>
+    <t>2026-05-11T14:42:24.030Z</t>
+  </si>
+  <si>
+    <t>Sage Prevalon Turn and Position System (TAP) 2.0 | Stryker</t>
+  </si>
+  <si>
+    <t>https://www.stryker.com/us/en/sage/products/sage-tap-2-0.html</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-tap-lc.report.json</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-tap-lc</t>
+  </si>
+  <si>
+    <t>2026-05-11T14:42:36.689Z</t>
+  </si>
+  <si>
+    <t>Sage TAP LC | Stryker</t>
+  </si>
+  <si>
+    <t>https://www.stryker.com/us/en/sage/products/sage-tap-lc.html</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-tap-xl-xxl.report.json</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-tap-xl-xxl</t>
+  </si>
+  <si>
+    <t>2026-05-11T14:42:47.258Z</t>
+  </si>
+  <si>
+    <t>Sage Prevalon Turn and Position System (TAP) XL/XXL | Stryker</t>
+  </si>
+  <si>
+    <t>https://www.stryker.com/us/en/sage/products/sage-tap-xl-xxl.html</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-traptex.report.json</t>
+  </si>
+  <si>
+    <t>us/en/sage/products/sage-traptex</t>
+  </si>
+  <si>
+    <t>2026-05-11T14:42:59.587Z</t>
+  </si>
+  <si>
+    <t>Sage Traptex Plumbing Protection System | Stryker</t>
+  </si>
+  <si>
+    <t>https://www.stryker.com/us/en/sage/products/sage-traptex.html</t>
   </si>
 </sst>
 </file>
@@ -465,12 +984,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="48" customWidth="1"/>
-    <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="36" customWidth="1"/>
+    <col min="1" max="3" width="50" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
     <col min="7" max="8" width="50" customWidth="1"/>
@@ -554,6 +1071,838 @@
         <v>21</v>
       </c>
     </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" t="s">
+        <v>55</v>
+      </c>
+      <c r="G9" t="s">
+        <v>56</v>
+      </c>
+      <c r="H9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" t="s">
+        <v>65</v>
+      </c>
+      <c r="G11" t="s">
+        <v>66</v>
+      </c>
+      <c r="H11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" t="s">
+        <v>70</v>
+      </c>
+      <c r="G12" t="s">
+        <v>71</v>
+      </c>
+      <c r="H12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" t="s">
+        <v>75</v>
+      </c>
+      <c r="G13" t="s">
+        <v>76</v>
+      </c>
+      <c r="H13" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" t="s">
+        <v>79</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" t="s">
+        <v>80</v>
+      </c>
+      <c r="G14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H14" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>83</v>
+      </c>
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" t="s">
+        <v>84</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" t="s">
+        <v>85</v>
+      </c>
+      <c r="G15" t="s">
+        <v>86</v>
+      </c>
+      <c r="H15" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>88</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" t="s">
+        <v>90</v>
+      </c>
+      <c r="G16" t="s">
+        <v>91</v>
+      </c>
+      <c r="H16" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>93</v>
+      </c>
+      <c r="B17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" t="s">
+        <v>94</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" t="s">
+        <v>95</v>
+      </c>
+      <c r="G17" t="s">
+        <v>96</v>
+      </c>
+      <c r="H17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>98</v>
+      </c>
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s">
+        <v>99</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" t="s">
+        <v>100</v>
+      </c>
+      <c r="G18" t="s">
+        <v>101</v>
+      </c>
+      <c r="H18" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>103</v>
+      </c>
+      <c r="B19" t="s">
+        <v>104</v>
+      </c>
+      <c r="C19" t="s">
+        <v>105</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" t="s">
+        <v>106</v>
+      </c>
+      <c r="G19" t="s">
+        <v>107</v>
+      </c>
+      <c r="H19" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>109</v>
+      </c>
+      <c r="B20" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" t="s">
+        <v>110</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" t="s">
+        <v>111</v>
+      </c>
+      <c r="G20" t="s">
+        <v>112</v>
+      </c>
+      <c r="H20" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>114</v>
+      </c>
+      <c r="B21" t="s">
+        <v>115</v>
+      </c>
+      <c r="C21" t="s">
+        <v>116</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" t="s">
+        <v>117</v>
+      </c>
+      <c r="G21" t="s">
+        <v>118</v>
+      </c>
+      <c r="H21" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>120</v>
+      </c>
+      <c r="B22" t="s">
+        <v>121</v>
+      </c>
+      <c r="C22" t="s">
+        <v>122</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" t="s">
+        <v>123</v>
+      </c>
+      <c r="G22" t="s">
+        <v>124</v>
+      </c>
+      <c r="H22" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>126</v>
+      </c>
+      <c r="B23" t="s">
+        <v>127</v>
+      </c>
+      <c r="C23" t="s">
+        <v>128</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" t="s">
+        <v>129</v>
+      </c>
+      <c r="G23" t="s">
+        <v>130</v>
+      </c>
+      <c r="H23" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>132</v>
+      </c>
+      <c r="B24" t="s">
+        <v>133</v>
+      </c>
+      <c r="C24" t="s">
+        <v>134</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" t="s">
+        <v>135</v>
+      </c>
+      <c r="G24" t="s">
+        <v>136</v>
+      </c>
+      <c r="H24" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>138</v>
+      </c>
+      <c r="B25" t="s">
+        <v>139</v>
+      </c>
+      <c r="C25" t="s">
+        <v>140</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" t="s">
+        <v>141</v>
+      </c>
+      <c r="G25" t="s">
+        <v>142</v>
+      </c>
+      <c r="H25" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>144</v>
+      </c>
+      <c r="B26" t="s">
+        <v>145</v>
+      </c>
+      <c r="C26" t="s">
+        <v>146</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" t="s">
+        <v>147</v>
+      </c>
+      <c r="G26" t="s">
+        <v>148</v>
+      </c>
+      <c r="H26" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>150</v>
+      </c>
+      <c r="B27" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27" t="s">
+        <v>151</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" t="s">
+        <v>152</v>
+      </c>
+      <c r="G27" t="s">
+        <v>153</v>
+      </c>
+      <c r="H27" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>155</v>
+      </c>
+      <c r="B28" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" t="s">
+        <v>156</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" t="s">
+        <v>157</v>
+      </c>
+      <c r="G28" t="s">
+        <v>158</v>
+      </c>
+      <c r="H28" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>160</v>
+      </c>
+      <c r="B29" t="s">
+        <v>121</v>
+      </c>
+      <c r="C29" t="s">
+        <v>161</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" t="s">
+        <v>162</v>
+      </c>
+      <c r="G29" t="s">
+        <v>163</v>
+      </c>
+      <c r="H29" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>165</v>
+      </c>
+      <c r="B30" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" t="s">
+        <v>166</v>
+      </c>
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30" t="s">
+        <v>167</v>
+      </c>
+      <c r="G30" t="s">
+        <v>168</v>
+      </c>
+      <c r="H30" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>170</v>
+      </c>
+      <c r="B31" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" t="s">
+        <v>171</v>
+      </c>
+      <c r="D31" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" t="s">
+        <v>172</v>
+      </c>
+      <c r="G31" t="s">
+        <v>173</v>
+      </c>
+      <c r="H31" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>175</v>
+      </c>
+      <c r="B32" t="s">
+        <v>29</v>
+      </c>
+      <c r="C32" t="s">
+        <v>176</v>
+      </c>
+      <c r="D32" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" t="s">
+        <v>177</v>
+      </c>
+      <c r="G32" t="s">
+        <v>178</v>
+      </c>
+      <c r="H32" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>180</v>
+      </c>
+      <c r="B33" t="s">
+        <v>47</v>
+      </c>
+      <c r="C33" t="s">
+        <v>181</v>
+      </c>
+      <c r="D33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" t="s">
+        <v>182</v>
+      </c>
+      <c r="G33" t="s">
+        <v>183</v>
+      </c>
+      <c r="H33" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>185</v>
+      </c>
+      <c r="B34" t="s">
+        <v>29</v>
+      </c>
+      <c r="C34" t="s">
+        <v>186</v>
+      </c>
+      <c r="D34" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" t="s">
+        <v>187</v>
+      </c>
+      <c r="G34" t="s">
+        <v>188</v>
+      </c>
+      <c r="H34" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>190</v>
+      </c>
+      <c r="B35" t="s">
+        <v>29</v>
+      </c>
+      <c r="C35" t="s">
+        <v>191</v>
+      </c>
+      <c r="D35" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" t="s">
+        <v>192</v>
+      </c>
+      <c r="G35" t="s">
+        <v>193</v>
+      </c>
+      <c r="H35" t="s">
+        <v>194</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
